--- a/output/roomself_excel/5065.xlsx
+++ b/output/roomself_excel/5065.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30846</v>
+        <v>193929</v>
       </c>
       <c r="D2" t="n">
-        <v>1412</v>
+        <v>3952</v>
       </c>
       <c r="E2" t="n">
-        <v>223</v>
+        <v>503</v>
       </c>
       <c r="F2" t="n">
-        <v>188</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32398</v>
+        <v>212914</v>
       </c>
       <c r="D3" t="n">
-        <v>1444</v>
+        <v>3757</v>
       </c>
       <c r="E3" t="n">
-        <v>167</v>
+        <v>545</v>
       </c>
       <c r="F3" t="n">
         <v>29</v>
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>489274</v>
+        <v>110476</v>
       </c>
       <c r="D4" t="n">
-        <v>8208</v>
+        <v>2692</v>
       </c>
       <c r="E4" t="n">
-        <v>841</v>
+        <v>284</v>
       </c>
       <c r="F4" t="n">
-        <v>561</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23074</v>
+        <v>114660</v>
       </c>
       <c r="D5" t="n">
-        <v>1220</v>
+        <v>2736</v>
       </c>
       <c r="E5" t="n">
-        <v>166</v>
+        <v>419</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6">
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>110476</v>
+        <v>108204</v>
       </c>
       <c r="D6" t="n">
-        <v>2692</v>
+        <v>2660</v>
       </c>
       <c r="E6" t="n">
         <v>284</v>
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>58647</v>
+        <v>32398</v>
       </c>
       <c r="D7" t="n">
-        <v>2048</v>
+        <v>1444</v>
       </c>
       <c r="E7" t="n">
-        <v>409</v>
+        <v>167</v>
       </c>
       <c r="F7" t="n">
-        <v>201</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>114660</v>
+        <v>23074</v>
       </c>
       <c r="D8" t="n">
-        <v>2736</v>
+        <v>1220</v>
       </c>
       <c r="E8" t="n">
-        <v>419</v>
+        <v>166</v>
       </c>
       <c r="F8" t="n">
-        <v>323</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108204</v>
+        <v>82431</v>
       </c>
       <c r="D9" t="n">
-        <v>2660</v>
+        <v>2620</v>
       </c>
       <c r="E9" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -655,6 +655,50 @@
         <v>169</v>
       </c>
       <c r="F10" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>30846</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1412</v>
+      </c>
+      <c r="E11" t="n">
+        <v>223</v>
+      </c>
+      <c r="F11" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>58647</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E12" t="n">
+        <v>173</v>
+      </c>
+      <c r="F12" t="n">
         <v>29</v>
       </c>
     </row>

--- a/output/roomself_excel/5065.xlsx
+++ b/output/roomself_excel/5065.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3952</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>503</v>
       </c>
-      <c r="F2" t="n">
-        <v>29</v>
-      </c>
+      <c r="G2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>3757</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>545</v>
       </c>
-      <c r="F3" t="n">
-        <v>29</v>
-      </c>
+      <c r="G3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +555,27 @@
       <c r="D4" t="n">
         <v>2692</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>284</v>
       </c>
-      <c r="F4" t="n">
-        <v>29</v>
+      <c r="G4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>389</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +593,27 @@
       <c r="D5" t="n">
         <v>2736</v>
       </c>
-      <c r="E5" t="n">
-        <v>419</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>323</v>
+        <v>390</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>294</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -563,10 +631,26 @@
       <c r="D6" t="n">
         <v>2660</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>381</v>
+      </c>
+      <c r="G6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>284</v>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
         <v>29</v>
       </c>
     </row>
@@ -585,12 +669,20 @@
       <c r="D7" t="n">
         <v>1444</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>167</v>
       </c>
-      <c r="F7" t="n">
-        <v>29</v>
-      </c>
+      <c r="G7" t="n">
+        <v>29</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +699,20 @@
       <c r="D8" t="n">
         <v>1220</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>166</v>
       </c>
-      <c r="F8" t="n">
-        <v>29</v>
-      </c>
+      <c r="G8" t="n">
+        <v>29</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +729,12 @@
       <c r="D9" t="n">
         <v>2620</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +751,20 @@
       <c r="D10" t="n">
         <v>1240</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>169</v>
       </c>
-      <c r="F10" t="n">
-        <v>29</v>
-      </c>
+      <c r="G10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +781,27 @@
       <c r="D11" t="n">
         <v>1412</v>
       </c>
-      <c r="E11" t="n">
-        <v>223</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>188</v>
+        <v>159</v>
+      </c>
+      <c r="G11" t="n">
+        <v>29</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>194</v>
+      </c>
+      <c r="J11" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +819,20 @@
       <c r="D12" t="n">
         <v>2048</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>173</v>
       </c>
-      <c r="F12" t="n">
-        <v>29</v>
-      </c>
+      <c r="G12" t="n">
+        <v>29</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/5065.xlsx
+++ b/output/roomself_excel/5065.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,26 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -509,6 +529,22 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>191</v>
+      </c>
+      <c r="N2" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -539,6 +575,22 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>282</v>
+      </c>
+      <c r="N3" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -577,6 +629,22 @@
       <c r="J4" t="n">
         <v>27</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>153</v>
+      </c>
+      <c r="N4" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -615,6 +683,22 @@
       <c r="J5" t="n">
         <v>29</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>151</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -653,6 +737,22 @@
       <c r="J6" t="n">
         <v>29</v>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>148</v>
+      </c>
+      <c r="N6" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -683,6 +783,22 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>65</v>
+      </c>
+      <c r="N7" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -713,6 +829,22 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>64</v>
+      </c>
+      <c r="N8" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -735,6 +867,10 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -765,6 +901,22 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>96</v>
+      </c>
+      <c r="N10" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -803,6 +955,22 @@
       <c r="J11" t="n">
         <v>29</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>61</v>
+      </c>
+      <c r="N11" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -833,6 +1001,22 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>85</v>
+      </c>
+      <c r="N12" t="n">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
